--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487904_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487904_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.8461</v>
+        <v>8.5883</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4545</v>
+        <v>4.549</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3916</v>
+        <v>4.0393</v>
       </c>
       <c r="G2" t="n">
         <v>3.5398</v>
@@ -610,13 +610,13 @@
         <v>1.2487</v>
       </c>
       <c r="S2" t="n">
-        <v>4.3033</v>
+        <v>2.0455</v>
       </c>
       <c r="T2" t="n">
-        <v>2.9442</v>
+        <v>1.0387</v>
       </c>
       <c r="U2" t="n">
-        <v>1.359</v>
+        <v>1.0067</v>
       </c>
       <c r="V2" t="n">
         <v>2.795</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.6744</v>
+        <v>4.852</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7588</v>
+        <v>2.3768</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9156</v>
+        <v>2.4752</v>
       </c>
       <c r="G3" t="n">
         <v>3.8658</v>
@@ -688,13 +688,13 @@
         <v>2.0812</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5547</v>
+        <v>0.7323</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9283</v>
+        <v>0.5463</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6264</v>
+        <v>0.186</v>
       </c>
       <c r="V3" t="n">
         <v>2.3351</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0219</v>
+        <v>3.8251</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3896</v>
+        <v>1.2516</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6323</v>
+        <v>2.5736</v>
       </c>
       <c r="G4" t="n">
         <v>2.7594</v>
@@ -766,13 +766,13 @@
         <v>1.6649</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8188</v>
+        <v>-0.0155</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3577</v>
+        <v>-0.4957</v>
       </c>
       <c r="U4" t="n">
-        <v>0.539</v>
+        <v>0.4802</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5838</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6599</v>
+        <v>0.9139</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0124</v>
+        <v>0.1195</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6475</v>
+        <v>0.7943</v>
       </c>
       <c r="G5" t="n">
         <v>0.7144</v>
@@ -844,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1755</v>
+        <v>0.4294</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0124</v>
+        <v>0.1195</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1631</v>
+        <v>0.3099</v>
       </c>
       <c r="V5" t="n">
         <v>-0.23</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MEGIAS</t>
+          <t>C. FIELDS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2904</v>
+        <v>0.3878</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2345</v>
+        <v>-0.8956</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5249</v>
+        <v>1.2835</v>
       </c>
       <c r="G6" t="n">
-        <v>5.0122</v>
+        <v>-2.6007</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5076</v>
+        <v>-1.5524</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5047</v>
+        <v>-1.0483</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6244</v>
+        <v>-1.7351</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8015</v>
+        <v>-1.2501</v>
       </c>
       <c r="L6" t="n">
-        <v>0.823</v>
+        <v>-0.485</v>
       </c>
       <c r="M6" t="n">
-        <v>1.3878</v>
+        <v>-0.8656</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7060999999999999</v>
+        <v>-0.3023</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6817</v>
+        <v>-0.5633</v>
       </c>
       <c r="P6" t="n">
-        <v>1.2487</v>
+        <v>2.2893</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.2487</v>
+        <v>2.2893</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5722</v>
+        <v>-0.4683</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0867</v>
+        <v>-0.3281</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6589</v>
+        <v>-0.1402</v>
       </c>
       <c r="V6" t="n">
-        <v>-5.9792</v>
+        <v>1.1675</v>
       </c>
       <c r="W6" t="n">
-        <v>-2.4766</v>
+        <v>1.1675</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.5026</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. MORENO POZA</t>
+          <t>I. CASAS GARRIDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3227</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5118</v>
+        <v>-0.8471</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8345</v>
+        <v>0.7814</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.8804999999999999</v>
+        <v>-0.4834</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0298</v>
+        <v>-0.2622</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8507</v>
+        <v>-0.2213</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0584</v>
+        <v>-0.6466</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0192</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0392</v>
+        <v>-0.7234</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9389</v>
+        <v>0.1632</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.049</v>
+        <v>-0.3389</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8899</v>
+        <v>0.5021</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3497</v>
+        <v>0.0233</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4534</v>
+        <v>-0.2005</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1037</v>
+        <v>0.2238</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. CASAS GARRIDO</t>
+          <t>J. MARTINEZ MEGIAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.348</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3643</v>
+        <v>1.2579</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0163</v>
+        <v>-1.3488</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4834</v>
+        <v>5.0122</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2622</v>
+        <v>3.5076</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2213</v>
+        <v>1.5047</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6466</v>
+        <v>3.6244</v>
       </c>
       <c r="K8" t="n">
-        <v>0.07679999999999999</v>
+        <v>2.8015</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7234</v>
+        <v>0.823</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1632</v>
+        <v>1.3878</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3389</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5021</v>
+        <v>0.6817</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.259</v>
+        <v>-0.3727</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7177</v>
+        <v>0.11</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4587</v>
+        <v>-0.4827</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.23</v>
+        <v>-5.9792</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-2.4766</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.23</v>
+        <v>-3.5026</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. LOPES MARQUES</t>
+          <t>J. MORENO POZA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8393</v>
+        <v>-0.3059</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8372000000000001</v>
+        <v>0.4699</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.002</v>
+        <v>-0.7758</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3813</v>
+        <v>-0.8804999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1322</v>
+        <v>-0.0298</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.249</v>
+        <v>-0.8507</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2067</v>
+        <v>0.0584</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2067</v>
+        <v>0.0192</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.0392</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5879</v>
+        <v>-0.9389</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3389</v>
+        <v>-0.049</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.249</v>
+        <v>-0.8899</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.4162</v>
+        <v>0.2081</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0418</v>
+        <v>0.3665</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0033</v>
+        <v>0.4115</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0385</v>
+        <v>-0.045</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. FIELDS</t>
+          <t>A. LOPES MARQUES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1148</v>
+        <v>-1.0135</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2515</v>
+        <v>-1.0701</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1367</v>
+        <v>0.0567</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.6007</v>
+        <v>-0.3813</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5524</v>
+        <v>-0.1322</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0483</v>
+        <v>-0.249</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7351</v>
+        <v>0.2067</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.2501</v>
+        <v>0.2067</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.485</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8656</v>
+        <v>-0.5879</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3023</v>
+        <v>-0.3389</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5633</v>
+        <v>-0.249</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2893</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2893</v>
+        <v>0.6244</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.9709</v>
+        <v>-0.216</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.6839</v>
+        <v>-0.2362</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.287</v>
+        <v>0.0202</v>
       </c>
       <c r="V10" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5633</v>
+        <v>-1.4288</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.63</v>
+        <v>0.3577</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9333</v>
+        <v>-1.7865</v>
       </c>
       <c r="G11" t="n">
         <v>-1.416</v>
@@ -1312,13 +1312,13 @@
         <v>1.2487</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2285</v>
+        <v>-0.0939</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7177</v>
+        <v>0.2701</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5108</v>
+        <v>-0.364</v>
       </c>
       <c r="V11" t="n">
         <v>-1.1675</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6755</v>
+        <v>-1.7277</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0265</v>
+        <v>-0.3135</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6491</v>
+        <v>-1.4142</v>
       </c>
       <c r="G12" t="n">
         <v>-3.9063</v>
@@ -1390,13 +1390,13 @@
         <v>1.8731</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8098</v>
+        <v>-0.862</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7862</v>
+        <v>-0.0733</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0236</v>
+        <v>-0.7887</v>
       </c>
       <c r="V12" t="n">
         <v>1.1675</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.8296</v>
+        <v>-2.4326</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.5606</v>
+        <v>-1.281</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.269</v>
+        <v>-1.1516</v>
       </c>
       <c r="G13" t="n">
         <v>-0.8956</v>
@@ -1468,13 +1468,13 @@
         <v>0.4162</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5989</v>
+        <v>-0.2019</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2486</v>
+        <v>0.031</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3503</v>
+        <v>-0.2329</v>
       </c>
       <c r="V13" t="n">
         <v>-1.7513</v>
@@ -1501,25 +1501,25 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.218699999999998</v>
+        <v>11.502</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6915</v>
+        <v>5.9751</v>
       </c>
       <c r="F14" t="n">
-        <v>5.5272</v>
+        <v>5.5271</v>
       </c>
       <c r="G14" t="n">
-        <v>5.3278</v>
+        <v>5.327800000000002</v>
       </c>
       <c r="H14" t="n">
-        <v>5.5115</v>
+        <v>5.511500000000001</v>
       </c>
       <c r="I14" t="n">
         <v>-0.1838000000000012</v>
       </c>
       <c r="J14" t="n">
-        <v>3.471600000000001</v>
+        <v>3.4716</v>
       </c>
       <c r="K14" t="n">
         <v>5.1251</v>
@@ -1534,7 +1534,7 @@
         <v>0.3864999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>1.469600000000001</v>
+        <v>1.4696</v>
       </c>
       <c r="P14" t="n">
         <v>7.2841</v>
@@ -1546,13 +1546,13 @@
         <v>13.5277</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9166999999999996</v>
+        <v>1.3667</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0901</v>
+        <v>1.1933</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1733999999999998</v>
+        <v>0.1733000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-2.476699999999999</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. BULTO CASTILLO</t>
+          <t>E. VAN DER HEIJDEN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9676</v>
+        <v>2.3095</v>
       </c>
       <c r="E15" t="n">
-        <v>3.503</v>
+        <v>0.3933</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5354</v>
+        <v>1.9162</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7958</v>
+        <v>1.284</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4242</v>
+        <v>1.5265</v>
       </c>
       <c r="I15" t="n">
-        <v>3.22</v>
+        <v>-0.2425</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9877</v>
+        <v>1.7987</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6568000000000001</v>
+        <v>2.4045</v>
       </c>
       <c r="L15" t="n">
-        <v>3.6445</v>
+        <v>-0.6058</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1919</v>
+        <v>-0.5147</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2326</v>
+        <v>-0.878</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4245</v>
+        <v>0.3633</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8325</v>
+        <v>-3.3299</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-4.3705</v>
       </c>
       <c r="R15" t="n">
-        <v>0.8325</v>
+        <v>1.0406</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5069</v>
+        <v>0.3751</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5153</v>
+        <v>0.0463</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.3289</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.1675</v>
+        <v>3.9802</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.9188</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1675</v>
+        <v>1.0614</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9711</v>
+        <v>2.2989</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3528</v>
+        <v>1.5672</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6182</v>
+        <v>0.7317</v>
       </c>
       <c r="G16" t="n">
         <v>-0.9092</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1624</v>
+        <v>0.1654</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3262</v>
+        <v>-0.1119</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1638</v>
+        <v>0.2773</v>
       </c>
       <c r="V16" t="n">
         <v>3.0427</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. VAN DER HEIJDEN</t>
+          <t>D. BULTO CASTILLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5912</v>
+        <v>2.2914</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0353</v>
+        <v>2.8601</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6266</v>
+        <v>-0.5687</v>
       </c>
       <c r="G17" t="n">
-        <v>1.284</v>
+        <v>2.7958</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5265</v>
+        <v>-0.4242</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.2425</v>
+        <v>3.22</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7987</v>
+        <v>2.9877</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4045</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6058</v>
+        <v>3.6445</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5147</v>
+        <v>-0.1919</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.878</v>
+        <v>0.2326</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3633</v>
+        <v>-0.4245</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.3299</v>
+        <v>0.8325</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.3705</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0406</v>
+        <v>0.8325</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3431</v>
+        <v>-0.1693</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3824</v>
+        <v>-0.1276</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0392</v>
+        <v>-0.0417</v>
       </c>
       <c r="V17" t="n">
-        <v>3.9802</v>
+        <v>-1.1675</v>
       </c>
       <c r="W17" t="n">
-        <v>2.9188</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.0614</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. AMADASUN</t>
+          <t>R. LLAMAS MARTINEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5911</v>
+        <v>1.3832</v>
       </c>
       <c r="E18" t="n">
-        <v>1.798</v>
+        <v>0.853</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2069</v>
+        <v>0.5301</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2164</v>
+        <v>1.2099</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5715</v>
+        <v>0.1706</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7879</v>
+        <v>1.0393</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1549</v>
+        <v>0.6916</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2243</v>
+        <v>0.6524</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0694</v>
+        <v>0.0392</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3713</v>
+        <v>0.5183</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3472</v>
+        <v>-0.4818</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7185</v>
+        <v>1.0001</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8325</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.6672</v>
+        <v>0.1732</v>
       </c>
       <c r="T18" t="n">
-        <v>2.8666</v>
+        <v>0.1615</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8006</v>
+        <v>0.0118</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0437</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.2112</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. LLAMAS MARTINEZ</t>
+          <t>J. LLAMAS PRADO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1395</v>
+        <v>-0.1534</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6387</v>
+        <v>-0.4038</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5008</v>
+        <v>0.2504</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2099</v>
+        <v>-1.2551</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1706</v>
+        <v>-2.0894</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0393</v>
+        <v>0.8344</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6916</v>
+        <v>-0.2343</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6524</v>
+        <v>-1.3136</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0392</v>
+        <v>1.0793</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5183</v>
+        <v>-1.0207</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4818</v>
+        <v>-0.7758</v>
       </c>
       <c r="O19" t="n">
-        <v>1.0001</v>
+        <v>-0.2449</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.2081</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.2081</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.4162</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0704</v>
+        <v>0.5397</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0529</v>
+        <v>0.0386</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0176</v>
+        <v>0.5011</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. LLAMAS PRADO</t>
+          <t>M. AMADASUN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.609</v>
+        <v>-0.4297</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.511</v>
+        <v>-0.1308</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.098</v>
+        <v>-0.2989</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2551</v>
+        <v>0.2164</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0894</v>
+        <v>-0.5715</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8344</v>
+        <v>0.7879</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2343</v>
+        <v>-0.1549</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3136</v>
+        <v>-0.2243</v>
       </c>
       <c r="L20" t="n">
-        <v>1.0793</v>
+        <v>0.0694</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0207</v>
+        <v>0.3713</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7758</v>
+        <v>-0.3472</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2449</v>
+        <v>0.7185</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2081</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2081</v>
+        <v>-2.0812</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4162</v>
+        <v>0.8325</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0842</v>
+        <v>1.6464</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.9378</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1527</v>
+        <v>0.7086</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3538</v>
+        <v>-1.0437</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3538</v>
+        <v>-2.2112</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. HAYMAN</t>
+          <t>D. CEBOLLA PORCAR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.186</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1073</v>
+        <v>-1.1307</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9212</v>
+        <v>0.61</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2642</v>
+        <v>1.8038</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1768</v>
+        <v>-0.2707</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.08740000000000001</v>
+        <v>2.0745</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4762</v>
+        <v>1.5796</v>
       </c>
       <c r="K21" t="n">
         <v>0.5093</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.9854000000000001</v>
+        <v>1.0703</v>
       </c>
       <c r="M21" t="n">
-        <v>0.212</v>
+        <v>0.2242</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6861</v>
+        <v>-0.78</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8981</v>
+        <v>1.0042</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4162</v>
+        <v>-2.7055</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.2487</v>
+        <v>-3.3299</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8325</v>
+        <v>0.6244</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5056</v>
+        <v>0.7348</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3824</v>
+        <v>0.3896</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1232</v>
+        <v>0.3452</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.3538</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. CEBOLLA PORCAR</t>
+          <t>D. HAYMAN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2502</v>
+        <v>-0.64</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0952</v>
+        <v>-1.6786</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8449</v>
+        <v>1.0387</v>
       </c>
       <c r="G22" t="n">
-        <v>1.8038</v>
+        <v>-0.2642</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2707</v>
+        <v>-0.1768</v>
       </c>
       <c r="I22" t="n">
-        <v>2.0745</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>1.5796</v>
+        <v>-0.4762</v>
       </c>
       <c r="K22" t="n">
         <v>0.5093</v>
       </c>
       <c r="L22" t="n">
-        <v>1.0703</v>
+        <v>-0.9854000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2242</v>
+        <v>0.212</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.78</v>
+        <v>-0.6861</v>
       </c>
       <c r="O22" t="n">
-        <v>1.0042</v>
+        <v>0.8981</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.7055</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.3299</v>
+        <v>-1.2487</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0053</v>
+        <v>0.0405</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5748</v>
+        <v>0.0463</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5800999999999999</v>
+        <v>-0.0058</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3538</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0169</v>
+        <v>-3.5565</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5568</v>
+        <v>-2.2353</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4601</v>
+        <v>-1.3211</v>
       </c>
       <c r="G23" t="n">
         <v>-3.6985</v>
@@ -2248,13 +2248,13 @@
         <v>0.6244</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9427</v>
+        <v>-0.4823</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1744</v>
+        <v>-0.8529</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2317</v>
+        <v>0.3706</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.1211</v>
+        <v>-3.9472</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0285</v>
+        <v>-2.4928</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0925</v>
+        <v>-1.4545</v>
       </c>
       <c r="G24" t="n">
         <v>-4.6071</v>
@@ -2326,13 +2326,13 @@
         <v>0.8325</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.952</v>
+        <v>-0.7782</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1744</v>
+        <v>-0.6385999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7776</v>
+        <v>-0.1396</v>
       </c>
       <c r="V24" t="n">
         <v>0.8137</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.2958</v>
+        <v>-6.8253</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.4856</v>
+        <v>-3.1285</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.8103</v>
+        <v>-3.6968</v>
       </c>
       <c r="G25" t="n">
         <v>-1.9036</v>
@@ -2404,13 +2404,13 @@
         <v>0.2081</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6296</v>
+        <v>0.1001</v>
       </c>
       <c r="T25" t="n">
-        <v>0.5806</v>
+        <v>-0.0624</v>
       </c>
       <c r="U25" t="n">
-        <v>0.049</v>
+        <v>0.1625</v>
       </c>
       <c r="V25" t="n">
         <v>-3.1488</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-9.218500000000001</v>
+        <v>-7.789800000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.5272</v>
+        <v>-5.526900000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.6915</v>
+        <v>-2.2629</v>
       </c>
       <c r="G26" t="n">
         <v>-5.327800000000001</v>
@@ -2452,13 +2452,13 @@
         <v>-5.5114</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1836000000000011</v>
+        <v>0.1836000000000002</v>
       </c>
       <c r="J26" t="n">
         <v>-1.856000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.3862000000000001</v>
+        <v>-0.3862000000000003</v>
       </c>
       <c r="L26" t="n">
         <v>-1.4696</v>
@@ -2467,13 +2467,13 @@
         <v>-3.4717</v>
       </c>
       <c r="N26" t="n">
-        <v>-5.1251</v>
+        <v>-5.125100000000001</v>
       </c>
       <c r="O26" t="n">
         <v>1.6534</v>
       </c>
       <c r="P26" t="n">
-        <v>-7.284</v>
+        <v>-7.284000000000001</v>
       </c>
       <c r="Q26" t="n">
         <v>-13.5277</v>
@@ -2482,16 +2482,16 @@
         <v>6.243699999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>0.9169999999999999</v>
+        <v>2.3454</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1735000000000004</v>
+        <v>-0.1733000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>1.0903</v>
+        <v>2.5189</v>
       </c>
       <c r="V26" t="n">
-        <v>2.4766</v>
+        <v>2.476599999999999</v>
       </c>
       <c r="W26" t="n">
         <v>10.0302</v>
